--- a/ig/document/StructureDefinition-medcom-document-practitionerrole.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1869,7 +1869,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>170</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>201</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>211</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>255</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>260</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>265</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>276</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>287</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>302</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>324</v>
       </c>
@@ -8353,12 +8353,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN59">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-practitionerrole.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
